--- a/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>63776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125259</t>
+          <t>127833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168004</t>
+          <t>172274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264983</t>
+          <t>265203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296594</t>
+          <t>298703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165211</t>
+          <t>166851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194816</t>
+          <t>194445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443953</t>
+          <t>439683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486698</t>
+          <t>484124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74822</t>
+          <t>72910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75157</t>
+          <t>73771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105743</t>
+          <t>105064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124475</t>
+          <t>127788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>171427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191357</t>
+          <t>193269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219924</t>
+          <t>221228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189501</t>
+          <t>190180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220087</t>
+          <t>221473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392985</t>
+          <t>389996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>436948</t>
+          <t>433635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82863</t>
+          <t>83188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>119043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56443</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123155</t>
+          <t>123946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166083</t>
+          <t>166303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317383</t>
+          <t>315283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351463</t>
+          <t>351138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>95488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117352</t>
+          <t>117946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>419442</t>
+          <t>419222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462370</t>
+          <t>461579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191592</t>
+          <t>190993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240749</t>
+          <t>244084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137569</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178917</t>
+          <t>178936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339444</t>
+          <t>341532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408481</t>
+          <t>405412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>742620</t>
+          <t>739285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>791777</t>
+          <t>792376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422517</t>
+          <t>422498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463865</t>
+          <t>464977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176322</t>
+          <t>1179391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1245359</t>
+          <t>1243271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>46295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109382</t>
+          <t>109033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149499</t>
+          <t>150163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>167099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216619</t>
+          <t>214448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195284</t>
+          <t>196073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221351</t>
+          <t>222841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>352599</t>
+          <t>351935</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392716</t>
+          <t>393065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>554615</t>
+          <t>556786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604889</t>
+          <t>604135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>237677</t>
+          <t>235561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292863</t>
+          <t>292995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261136</t>
+          <t>261349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320927</t>
+          <t>319948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110542</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128438</t>
+          <t>128812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>780064</t>
+          <t>779932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>835250</t>
+          <t>837366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>897156</t>
+          <t>898135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956947</t>
+          <t>956734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>495698</t>
+          <t>501252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>583275</t>
+          <t>583018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>705637</t>
+          <t>704477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>800830</t>
+          <t>799555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1219949</t>
+          <t>1226400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1347438</t>
+          <t>1350393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1877370</t>
+          <t>1877627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1964947</t>
+          <t>1959393</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2071550</t>
+          <t>2072825</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2166743</t>
+          <t>2167903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3985587</t>
+          <t>3982632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4113076</t>
+          <t>4106625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>152656</t>
+          <t>148859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192140</t>
+          <t>189246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132619</t>
+          <t>134189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167689</t>
+          <t>167372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>296712</t>
+          <t>293661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>348410</t>
+          <t>346494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147476</t>
+          <t>150370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186960</t>
+          <t>190757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94876</t>
+          <t>95193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129946</t>
+          <t>128376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253771</t>
+          <t>255687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>305469</t>
+          <t>308520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153427</t>
+          <t>154431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195199</t>
+          <t>194850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172802</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207872</t>
+          <t>204737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>337508</t>
+          <t>336073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390012</t>
+          <t>393241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156763</t>
+          <t>157112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>198535</t>
+          <t>197531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93110</t>
+          <t>96245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>130650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>262932</t>
+          <t>259703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315436</t>
+          <t>316871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>244824</t>
+          <t>245288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292664</t>
+          <t>289570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109504</t>
+          <t>109629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141504</t>
+          <t>141444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>367462</t>
+          <t>364105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424595</t>
+          <t>420530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231506</t>
+          <t>234600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279346</t>
+          <t>278882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92933</t>
+          <t>92993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334012</t>
+          <t>338077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391145</t>
+          <t>394502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491797</t>
+          <t>492421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>554707</t>
+          <t>556242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>375819</t>
+          <t>376863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>430969</t>
+          <t>426904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>887191</t>
+          <t>884887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>964084</t>
+          <t>968168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406204</t>
+          <t>404669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469114</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227920</t>
+          <t>231985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283070</t>
+          <t>282026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655717</t>
+          <t>651633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732610</t>
+          <t>734914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194690</t>
+          <t>194853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234121</t>
+          <t>237400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>374767</t>
+          <t>374349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>427275</t>
+          <t>430794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>584627</t>
+          <t>580451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>649567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180145</t>
+          <t>176866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219576</t>
+          <t>219413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275815</t>
+          <t>272296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328323</t>
+          <t>328741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467023</t>
+          <t>467789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>532729</t>
+          <t>536905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59893</t>
+          <t>59881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84836</t>
+          <t>84663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>400349</t>
+          <t>397350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>461076</t>
+          <t>466279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>469279</t>
+          <t>469916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>536544</t>
+          <t>538239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68546</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>93501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514358</t>
+          <t>509155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>575085</t>
+          <t>578084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>592273</t>
+          <t>590578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659538</t>
+          <t>658901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1367898</t>
+          <t>1375936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1474059</t>
+          <t>1479626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1639148</t>
+          <t>1637716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1754837</t>
+          <t>1754669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3042465</t>
+          <t>3045600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3202261</t>
+          <t>3199012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1270248</t>
+          <t>1264681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1376409</t>
+          <t>1368371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1380561</t>
+          <t>1380729</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1496250</t>
+          <t>1497682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2677444</t>
+          <t>2680693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2837240</t>
+          <t>2834105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101584</t>
+          <t>103162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136468</t>
+          <t>136601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124421</t>
+          <t>122826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157803</t>
+          <t>157272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234794</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285913</t>
+          <t>283141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152407</t>
+          <t>152274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187291</t>
+          <t>185713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116272</t>
+          <t>116803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149654</t>
+          <t>151249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277037</t>
+          <t>279809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>328156</t>
+          <t>326418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115498</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150368</t>
+          <t>148135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154156</t>
+          <t>152993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188409</t>
+          <t>188082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278053</t>
+          <t>279614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328062</t>
+          <t>326584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132354</t>
+          <t>134587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167224</t>
+          <t>167552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115874</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150127</t>
+          <t>151290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258942</t>
+          <t>260420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308951</t>
+          <t>307390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160255</t>
+          <t>160606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201644</t>
+          <t>201101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>79169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223879</t>
+          <t>221776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272502</t>
+          <t>271149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220767</t>
+          <t>221310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262156</t>
+          <t>261805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69460</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95571</t>
+          <t>96271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299690</t>
+          <t>301043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>348313</t>
+          <t>350416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316390</t>
+          <t>316048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373875</t>
+          <t>374043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>325688</t>
+          <t>325993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>378272</t>
+          <t>376115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>655449</t>
+          <t>661752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>736561</t>
+          <t>739404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498956</t>
+          <t>498788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556441</t>
+          <t>556783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277727</t>
+          <t>279884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330311</t>
+          <t>330006</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>792268</t>
+          <t>789425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>873380</t>
+          <t>867077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186801</t>
+          <t>185922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229977</t>
+          <t>230612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>279465</t>
+          <t>279367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>330575</t>
+          <t>331095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>478892</t>
+          <t>477833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>546330</t>
+          <t>547412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250728</t>
+          <t>250093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293904</t>
+          <t>294783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328916</t>
+          <t>328396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380026</t>
+          <t>380124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>593866</t>
+          <t>592784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>661304</t>
+          <t>662363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68411</t>
+          <t>68812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315675</t>
+          <t>314456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>376063</t>
+          <t>373982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>370189</t>
+          <t>368014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>434184</t>
+          <t>436927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81907</t>
+          <t>81506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105693</t>
+          <t>104634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>523435</t>
+          <t>525516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583823</t>
+          <t>585042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615632</t>
+          <t>612889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>679627</t>
+          <t>681802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>987630</t>
+          <t>992598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1087944</t>
+          <t>1093651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1328847</t>
+          <t>1324977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1439571</t>
+          <t>1435480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2350846</t>
+          <t>2344664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2494054</t>
+          <t>2497812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1409917</t>
+          <t>1404210</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1510231</t>
+          <t>1505263</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1503556</t>
+          <t>1507647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1614280</t>
+          <t>1618150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2946933</t>
+          <t>2943175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3090141</t>
+          <t>3096323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53615</t>
+          <t>50967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84059</t>
+          <t>82371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59633</t>
+          <t>60655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86211</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119703</t>
+          <t>119765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158323</t>
+          <t>158678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267750</t>
+          <t>269438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298194</t>
+          <t>300842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238390</t>
+          <t>237717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264968</t>
+          <t>263946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518086</t>
+          <t>517731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556706</t>
+          <t>556644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71580</t>
+          <t>71837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80099</t>
+          <t>78604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107687</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144576</t>
+          <t>144994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217104</t>
+          <t>216847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243302</t>
+          <t>243994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200648</t>
+          <t>202143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>223577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424855</t>
+          <t>424437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461744</t>
+          <t>459811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99481</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101446</t>
+          <t>100554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135615</t>
+          <t>134654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210213</t>
+          <t>211254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239173</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>93526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109072</t>
+          <t>109074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308248</t>
+          <t>309209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342417</t>
+          <t>343309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156083</t>
+          <t>155781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202579</t>
+          <t>202139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175313</t>
+          <t>175271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>573029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350224</t>
+          <t>352371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>868149</t>
+          <t>901720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505052</t>
+          <t>505492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551548</t>
+          <t>551850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200701</t>
+          <t>217707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615423</t>
+          <t>615465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630218</t>
+          <t>596647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1148143</t>
+          <t>1145996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58692</t>
+          <t>59315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89077</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130169</t>
+          <t>136563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>216895</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207480</t>
+          <t>191508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289486</t>
+          <t>292266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>253577</t>
+          <t>253465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283962</t>
+          <t>283339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489902</t>
+          <t>486255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>576628</t>
+          <t>570234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>759965</t>
+          <t>757185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>841971</t>
+          <t>857943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>178723</t>
+          <t>176264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218376</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192941</t>
+          <t>194168</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238380</t>
+          <t>240897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75642</t>
+          <t>73252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97095</t>
+          <t>96440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>364822</t>
+          <t>367208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>404475</t>
+          <t>406934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451247</t>
+          <t>448730</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496686</t>
+          <t>495459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>439644</t>
+          <t>443163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>517524</t>
+          <t>515755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>722636</t>
+          <t>725908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1350532</t>
+          <t>1347730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1189927</t>
+          <t>1194835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1896268</t>
+          <t>1969747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1589377</t>
+          <t>1591146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1667257</t>
+          <t>1663738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1469715</t>
+          <t>1472517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2097611</t>
+          <t>2094339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3030881</t>
+          <t>2957402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3737222</t>
+          <t>3732314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63776</t>
+          <t>64950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97276</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82627</t>
+          <t>81021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127833</t>
+          <t>126154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172274</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265203</t>
+          <t>264137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298703</t>
+          <t>297529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166851</t>
+          <t>168457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194445</t>
+          <t>195746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439683</t>
+          <t>442142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484124</t>
+          <t>485803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72910</t>
+          <t>75215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73771</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105064</t>
+          <t>104895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127788</t>
+          <t>126099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171427</t>
+          <t>167397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193269</t>
+          <t>190964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221228</t>
+          <t>220349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190180</t>
+          <t>190349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221473</t>
+          <t>221067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389996</t>
+          <t>394026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>433635</t>
+          <t>435324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83188</t>
+          <t>81249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119043</t>
+          <t>116776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123946</t>
+          <t>122159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166303</t>
+          <t>164728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315283</t>
+          <t>317550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351138</t>
+          <t>353077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95488</t>
+          <t>95098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117946</t>
+          <t>118803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>419222</t>
+          <t>420797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461579</t>
+          <t>463366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190993</t>
+          <t>192033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244084</t>
+          <t>241512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136457</t>
+          <t>136054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178936</t>
+          <t>178816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341532</t>
+          <t>341006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405412</t>
+          <t>404338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>739285</t>
+          <t>741857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792376</t>
+          <t>791336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422498</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464977</t>
+          <t>465380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1179391</t>
+          <t>1180465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1243271</t>
+          <t>1243797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>74621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109033</t>
+          <t>110129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150163</t>
+          <t>149623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167099</t>
+          <t>164141</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214448</t>
+          <t>213940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196073</t>
+          <t>194515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222841</t>
+          <t>222362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351935</t>
+          <t>352475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393065</t>
+          <t>391969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>556786</t>
+          <t>557294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604135</t>
+          <t>607093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>235561</t>
+          <t>237942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292995</t>
+          <t>294482</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261349</t>
+          <t>261043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>319948</t>
+          <t>320925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110607</t>
+          <t>110572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>129120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>779932</t>
+          <t>778445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>837366</t>
+          <t>834985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898135</t>
+          <t>897158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956734</t>
+          <t>957040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>501252</t>
+          <t>496330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>583018</t>
+          <t>581088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>704477</t>
+          <t>705289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>799555</t>
+          <t>803277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1226400</t>
+          <t>1229267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1350393</t>
+          <t>1352926</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1877627</t>
+          <t>1879557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1959393</t>
+          <t>1964315</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2072825</t>
+          <t>2069103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2167903</t>
+          <t>2167091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3982632</t>
+          <t>3980099</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4106625</t>
+          <t>4103758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148859</t>
+          <t>151777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189246</t>
+          <t>189492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>132432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167372</t>
+          <t>167799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>293661</t>
+          <t>297483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346494</t>
+          <t>346915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150370</t>
+          <t>150124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190757</t>
+          <t>187839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95193</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128376</t>
+          <t>130133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255687</t>
+          <t>255266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>308520</t>
+          <t>304698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154431</t>
+          <t>152941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>194850</t>
+          <t>191962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170332</t>
+          <t>171326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204737</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>336073</t>
+          <t>335824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393241</t>
+          <t>389847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157112</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>197531</t>
+          <t>199021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96245</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130650</t>
+          <t>129656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259703</t>
+          <t>263097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316871</t>
+          <t>317120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245288</t>
+          <t>244956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289570</t>
+          <t>292387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141444</t>
+          <t>141385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364105</t>
+          <t>364826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420530</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234600</t>
+          <t>231783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278882</t>
+          <t>279214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92993</t>
+          <t>93052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124808</t>
+          <t>125161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338077</t>
+          <t>337837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>394502</t>
+          <t>393781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>492421</t>
+          <t>493974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>556242</t>
+          <t>555137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>376863</t>
+          <t>375670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>426904</t>
+          <t>428075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884887</t>
+          <t>884785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>968168</t>
+          <t>969289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404669</t>
+          <t>405774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>468490</t>
+          <t>466937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231985</t>
+          <t>230814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282026</t>
+          <t>283219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651633</t>
+          <t>650512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734914</t>
+          <t>735016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194853</t>
+          <t>193749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237400</t>
+          <t>234387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>374349</t>
+          <t>373345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430794</t>
+          <t>426966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580451</t>
+          <t>583060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>649567</t>
+          <t>649541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>176866</t>
+          <t>179879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219413</t>
+          <t>220517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>272296</t>
+          <t>276124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328741</t>
+          <t>329745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467789</t>
+          <t>467815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>536905</t>
+          <t>534296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>84882</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>397350</t>
+          <t>401683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>466279</t>
+          <t>465360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>469916</t>
+          <t>469121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>538239</t>
+          <t>535211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68719</t>
+          <t>68500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>509155</t>
+          <t>510074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>578084</t>
+          <t>573751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>590578</t>
+          <t>593606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>658901</t>
+          <t>659696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1375936</t>
+          <t>1367767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1479626</t>
+          <t>1474639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1637716</t>
+          <t>1643371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1754669</t>
+          <t>1757053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3045600</t>
+          <t>3037623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3199012</t>
+          <t>3192617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1264681</t>
+          <t>1269668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1368371</t>
+          <t>1376540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1380729</t>
+          <t>1378345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1497682</t>
+          <t>1492027</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2680693</t>
+          <t>2687088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2834105</t>
+          <t>2842082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103162</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136601</t>
+          <t>137705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122826</t>
+          <t>124419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157272</t>
+          <t>158999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236532</t>
+          <t>235916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283141</t>
+          <t>284460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152274</t>
+          <t>151170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185713</t>
+          <t>186896</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116803</t>
+          <t>115076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151249</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279809</t>
+          <t>278490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>326418</t>
+          <t>327034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115170</t>
+          <t>112873</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148135</t>
+          <t>148462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152993</t>
+          <t>153720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188082</t>
+          <t>188057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279614</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326584</t>
+          <t>329626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134587</t>
+          <t>134260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167552</t>
+          <t>169849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>116226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151290</t>
+          <t>150563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260420</t>
+          <t>257378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>307390</t>
+          <t>307038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160606</t>
+          <t>160919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201101</t>
+          <t>202351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53510</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79169</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221776</t>
+          <t>223111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271149</t>
+          <t>269721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221310</t>
+          <t>220060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261805</t>
+          <t>261492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96271</t>
+          <t>98037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301043</t>
+          <t>302471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350416</t>
+          <t>349081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316048</t>
+          <t>312310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>374043</t>
+          <t>372831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>325993</t>
+          <t>325866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>376115</t>
+          <t>378668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>661752</t>
+          <t>657765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>739404</t>
+          <t>742587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498788</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556783</t>
+          <t>560521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279884</t>
+          <t>277331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330006</t>
+          <t>330133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>789425</t>
+          <t>786242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>867077</t>
+          <t>871064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185922</t>
+          <t>187570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230612</t>
+          <t>229837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>279367</t>
+          <t>279270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>328364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>477833</t>
+          <t>478037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>250868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294783</t>
+          <t>293135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328396</t>
+          <t>331127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380124</t>
+          <t>380221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>592784</t>
+          <t>592425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662363</t>
+          <t>662159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68812</t>
+          <t>68617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>314456</t>
+          <t>314347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>373417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>368014</t>
+          <t>366537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>436927</t>
+          <t>434285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81506</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104634</t>
+          <t>106288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>525516</t>
+          <t>526081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>585042</t>
+          <t>585151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>612889</t>
+          <t>615531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>681802</t>
+          <t>683279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>992598</t>
+          <t>990293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1093651</t>
+          <t>1094127</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1324977</t>
+          <t>1322793</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1435480</t>
+          <t>1437496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2344664</t>
+          <t>2350654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2497812</t>
+          <t>2497367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1404210</t>
+          <t>1403734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1505263</t>
+          <t>1507568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1507647</t>
+          <t>1505631</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1618150</t>
+          <t>1620334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2943175</t>
+          <t>2943620</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3096323</t>
+          <t>3090333</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66316</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>60141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82371</t>
+          <t>92552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60655</t>
+          <t>66884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86884</t>
+          <t>95123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>138480</t>
+          <t>155886</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119765</t>
+          <t>135417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158678</t>
+          <t>180060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>285493</t>
+          <t>304451</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269438</t>
+          <t>287784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300842</t>
+          <t>320195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252437</t>
+          <t>276937</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237717</t>
+          <t>261815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263946</t>
+          <t>290054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>537929</t>
+          <t>581387</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517731</t>
+          <t>557213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556644</t>
+          <t>601856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>351809</t>
+          <t>380336</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>351809</t>
+          <t>380336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>351809</t>
+          <t>380336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>324601</t>
+          <t>356938</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>324601</t>
+          <t>356938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>324601</t>
+          <t>356938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>676409</t>
+          <t>737273</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676409</t>
+          <t>737273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>676409</t>
+          <t>737273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44690</t>
+          <t>51084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71837</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57170</t>
+          <t>64559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>90688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>125735</t>
+          <t>141319</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109620</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144994</t>
+          <t>162108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230750</t>
+          <t>243565</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216847</t>
+          <t>227189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243994</t>
+          <t>257224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>212946</t>
+          <t>235241</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202143</t>
+          <t>221129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223577</t>
+          <t>247258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>443696</t>
+          <t>478806</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424437</t>
+          <t>458017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459811</t>
+          <t>497855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>288684</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>288684</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>288684</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>280747</t>
+          <t>311817</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>280747</t>
+          <t>311817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280747</t>
+          <t>311817</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>569431</t>
+          <t>620125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>569431</t>
+          <t>620125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>569431</t>
+          <t>620125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84893</t>
+          <t>97519</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>115750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>27474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>117034</t>
+          <t>133284</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100554</t>
+          <t>117953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134654</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>224801</t>
+          <t>250300</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211254</t>
+          <t>232069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>240108</t>
+          <t>265686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102028</t>
+          <t>114604</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>106274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109074</t>
+          <t>122894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>326829</t>
+          <t>364904</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309209</t>
+          <t>342343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343309</t>
+          <t>380235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>309694</t>
+          <t>347819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>309694</t>
+          <t>347819</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>309694</t>
+          <t>347819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134169</t>
+          <t>150368</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134169</t>
+          <t>150368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134169</t>
+          <t>150368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>443863</t>
+          <t>498188</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>443863</t>
+          <t>498188</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>443863</t>
+          <t>498188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>207177</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155781</t>
+          <t>181942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202139</t>
+          <t>234443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>339604</t>
+          <t>153211</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175271</t>
+          <t>135177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>573029</t>
+          <t>171607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>518055</t>
+          <t>360388</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352371</t>
+          <t>330259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>901720</t>
+          <t>395867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>529180</t>
+          <t>572724</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505492</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551850</t>
+          <t>597959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>451132</t>
+          <t>501193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217707</t>
+          <t>482797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615465</t>
+          <t>519227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>980312</t>
+          <t>1073917</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596647</t>
+          <t>1038438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1145996</t>
+          <t>1104046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>707631</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>707631</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>707631</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>790736</t>
+          <t>654404</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>790736</t>
+          <t>654404</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>790736</t>
+          <t>654404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1498367</t>
+          <t>1434305</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1498367</t>
+          <t>1434305</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1498367</t>
+          <t>1434305</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59315</t>
+          <t>65973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89189</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>185039</t>
+          <t>213869</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>196513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220542</t>
+          <t>235713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>295482</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191508</t>
+          <t>269825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292266</t>
+          <t>322433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>270413</t>
+          <t>307108</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>253465</t>
+          <t>288434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283339</t>
+          <t>322747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>521758</t>
+          <t>465581</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486255</t>
+          <t>443737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>570234</t>
+          <t>482937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>792171</t>
+          <t>772688</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>757185</t>
+          <t>745737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>857943</t>
+          <t>798345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342654</t>
+          <t>388720</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>342654</t>
+          <t>388720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>342654</t>
+          <t>388720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>706797</t>
+          <t>679450</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>706797</t>
+          <t>679450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>706797</t>
+          <t>679450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1049451</t>
+          <t>1068170</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1049451</t>
+          <t>1068170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1049451</t>
+          <t>1068170</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>196985</t>
+          <t>223683</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>176264</t>
+          <t>203347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>246826</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>215079</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194168</t>
+          <t>222261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240897</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>88335</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73252</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96440</t>
+          <t>88996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>386213</t>
+          <t>427428</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367208</t>
+          <t>404285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>406934</t>
+          <t>447764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>474548</t>
+          <t>505941</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>448730</t>
+          <t>480975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495459</t>
+          <t>531799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106429</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106429</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106429</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>583198</t>
+          <t>651111</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>583198</t>
+          <t>651111</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>583198</t>
+          <t>651111</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>689627</t>
+          <t>754060</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>689627</t>
+          <t>754060</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>689627</t>
+          <t>754060</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>477929</t>
+          <t>551372</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>443163</t>
+          <t>511313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>515755</t>
+          <t>592681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>893734</t>
+          <t>783104</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>725908</t>
+          <t>744021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1347730</t>
+          <t>828856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1371663</t>
+          <t>1334476</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1194835</t>
+          <t>1273159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1969747</t>
+          <t>1394291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1628972</t>
+          <t>1756661</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1591146</t>
+          <t>1715352</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1663738</t>
+          <t>1796720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1926513</t>
+          <t>2020984</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1472517</t>
+          <t>1975232</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2094339</t>
+          <t>2060067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3555486</t>
+          <t>3777645</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2957402</t>
+          <t>3717830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3732314</t>
+          <t>3838962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2106901</t>
+          <t>2308033</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2106901</t>
+          <t>2308033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2106901</t>
+          <t>2308033</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2820247</t>
+          <t>2804088</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2820247</t>
+          <t>2804088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2820247</t>
+          <t>2804088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4927149</t>
+          <t>5112121</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4927149</t>
+          <t>5112121</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4927149</t>
+          <t>5112121</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
